--- a/data/trans_orig/P6905-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6905-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29866</t>
+          <t>29972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58997</t>
+          <t>59061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73257</t>
+          <t>73533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81706</t>
+          <t>81600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98529</t>
+          <t>98544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>31980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54807</t>
+          <t>56318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28206</t>
+          <t>28649</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52376</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78533</t>
+          <t>77908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91174</t>
+          <t>89663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114879</t>
+          <t>114001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38326</t>
+          <t>38364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120244</t>
+          <t>120869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146401</t>
+          <t>148354</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23589</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44586</t>
+          <t>44019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43047</t>
+          <t>43376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68172</t>
+          <t>69307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65358</t>
+          <t>65925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86355</t>
+          <t>87460</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>31793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88305</t>
+          <t>87170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113430</t>
+          <t>113101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41856</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65707</t>
+          <t>65697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>30776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48839</t>
+          <t>48532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77862</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107605</t>
+          <t>107628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71342</t>
+          <t>71352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95193</t>
+          <t>94206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39712</t>
+          <t>40019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58296</t>
+          <t>57775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117995</t>
+          <t>117972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147738</t>
+          <t>148040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120280</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163652</t>
+          <t>166150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77154</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209046</t>
+          <t>204964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>259159</t>
+          <t>256786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308653</t>
+          <t>306155</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>352025</t>
+          <t>348534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115880</t>
+          <t>115220</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142967</t>
+          <t>144119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433268</t>
+          <t>435641</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>483381</t>
+          <t>487463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012 (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27810</t>
+          <t>28453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27190</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>48155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48770</t>
+          <t>48127</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63564</t>
+          <t>63584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62320</t>
+          <t>62687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83652</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30394</t>
+          <t>31595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>40667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64532</t>
+          <t>65278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60384</t>
+          <t>59183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76962</t>
+          <t>76392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39862</t>
+          <t>40338</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89744</t>
+          <t>88998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114087</t>
+          <t>113609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34015</t>
+          <t>33351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30261</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53222</t>
+          <t>53088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45542</t>
+          <t>46206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63288</t>
+          <t>63227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>28791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42241</t>
+          <t>42010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79314</t>
+          <t>79448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102275</t>
+          <t>101981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26432</t>
+          <t>27272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32033</t>
+          <t>32614</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31241</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>53072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52000</t>
+          <t>51160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66993</t>
+          <t>66511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32063</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48593</t>
+          <t>48263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>89283</t>
+          <t>89457</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111288</t>
+          <t>111913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102071</t>
+          <t>100601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74043</t>
+          <t>72440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103828</t>
+          <t>103677</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150211</t>
+          <t>152744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>195919</t>
+          <t>193169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>223276</t>
+          <t>224746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255696</t>
+          <t>255659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111007</t>
+          <t>111158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140792</t>
+          <t>142395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>344263</t>
+          <t>347013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>389971</t>
+          <t>387438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>18138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35803</t>
+          <t>35535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>34024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47353</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48785</t>
+          <t>49053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65996</t>
+          <t>66450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30423</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25860</t>
+          <t>24701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27909</t>
+          <t>29002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>52451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66561</t>
+          <t>67239</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84558</t>
+          <t>84448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29692</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43737</t>
+          <t>44414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100498</t>
+          <t>100084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124626</t>
+          <t>123533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>80,99%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43954</t>
+          <t>44399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35373</t>
+          <t>36098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48951</t>
+          <t>48906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>74240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65981</t>
+          <t>65536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85170</t>
+          <t>85084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>28649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44533</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100673</t>
+          <t>100442</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125731</t>
+          <t>125776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>19800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37546</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22086</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39541</t>
+          <t>40024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71511</t>
+          <t>71944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50864</t>
+          <t>51063</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69255</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26542</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43997</t>
+          <t>43747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>82549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107489</t>
+          <t>107560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80193</t>
+          <t>78681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114490</t>
+          <t>112585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75682</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104613</t>
+          <t>104549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160012</t>
+          <t>162076</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>206249</t>
+          <t>208156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>235511</t>
+          <t>237416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>269808</t>
+          <t>271320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111685</t>
+          <t>111749</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140616</t>
+          <t>141769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>360050</t>
+          <t>358143</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>406287</t>
+          <t>404223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21273</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18559</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37815</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49524</t>
+          <t>49478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66224</t>
+          <t>66450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33408</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43856</t>
+          <t>44438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88082</t>
+          <t>86826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107338</t>
+          <t>107481</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>16495</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37644</t>
+          <t>37309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26043</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43094</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>47412</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74218</t>
+          <t>72933</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74339</t>
+          <t>74674</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96492</t>
+          <t>95488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55636</t>
+          <t>56269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72335</t>
+          <t>72687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136494</t>
+          <t>137779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162803</t>
+          <t>163300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45123</t>
+          <t>45829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53245</t>
+          <t>54710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37730</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>49706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51785</t>
+          <t>51079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87007</t>
+          <t>86461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98939</t>
+          <t>97474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133807</t>
+          <t>134244</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>21025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40702</t>
+          <t>42073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48925</t>
+          <t>49393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54231</t>
+          <t>53521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83214</t>
+          <t>81656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60328</t>
+          <t>58957</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80218</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54971</t>
+          <t>54503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75998</t>
+          <t>75861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121712</t>
+          <t>123270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150695</t>
+          <t>151405</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60738</t>
+          <t>62196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99292</t>
+          <t>97889</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>82978</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135810</t>
+          <t>136476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>160841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>218460</t>
+          <t>220170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>240213</t>
+          <t>241616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>278767</t>
+          <t>277309</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>218405</t>
+          <t>217739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>270366</t>
+          <t>271237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>475260</t>
+          <t>473550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>533264</t>
+          <t>532879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
